--- a/local/agegroups/BARS-Results-2026-08.xlsx
+++ b/local/agegroups/BARS-Results-2026-08.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10525"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="10613"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/scottgonzalez/Projects/nemikor/usaw-owlcms/local/agegroups/"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{6518428C-BF79-1240-BCF8-8A16AA6E9066}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{8C6F72A0-2304-5E4B-9E50-02259E0B2882}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="1540" yWindow="600" windowWidth="39500" windowHeight="25100" tabRatio="500" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -36,7 +36,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="124" uniqueCount="41">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="132" uniqueCount="42">
   <si>
     <t>code</t>
   </si>
@@ -159,6 +159,9 @@
   </si>
   <si>
     <t>Masters</t>
+  </si>
+  <si>
+    <t>U11</t>
   </si>
 </sst>
 </file>
@@ -498,7 +501,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:W34"/>
+  <dimension ref="A1:W36"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="14.5" defaultRowHeight="13" x14ac:dyDescent="0.15"/>
   <cols>
     <col min="2" max="2" width="23.5" customWidth="1"/>
@@ -546,7 +549,7 @@
     </row>
     <row r="2" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A2" s="1" t="s">
-        <v>10</v>
+        <v>41</v>
       </c>
       <c r="B2" s="1" t="s">
         <v>38</v>
@@ -561,7 +564,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="4">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="G2" s="5" t="b">
         <f>TRUE()</f>
@@ -605,7 +608,7 @@
     </row>
     <row r="3" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A3" s="1" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="B3" s="1" t="s">
         <v>38</v>
@@ -617,16 +620,24 @@
         <v>9</v>
       </c>
       <c r="E3" s="4">
-        <v>14</v>
+        <v>12</v>
       </c>
       <c r="F3" s="4">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="G3" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H3" s="1"/>
+      <c r="H3" s="2">
+        <v>30</v>
+      </c>
+      <c r="I3" s="2">
+        <v>33</v>
+      </c>
+      <c r="J3">
+        <v>37</v>
+      </c>
       <c r="K3">
         <v>41</v>
       </c>
@@ -646,21 +657,17 @@
         <v>61</v>
       </c>
       <c r="Q3" s="1">
-        <v>69</v>
-      </c>
-      <c r="R3" s="1">
-        <v>77</v>
-      </c>
-      <c r="S3" s="1">
-        <v>999</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="S3" s="1"/>
+      <c r="T3" s="1"/>
       <c r="U3" s="1"/>
       <c r="V3" s="1"/>
       <c r="W3" s="1"/>
     </row>
     <row r="4" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A4" s="1" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="B4" s="1" t="s">
         <v>38</v>
@@ -672,16 +679,19 @@
         <v>9</v>
       </c>
       <c r="E4" s="4">
-        <v>16</v>
+        <v>14</v>
       </c>
       <c r="F4" s="4">
-        <v>17</v>
+        <v>15</v>
       </c>
       <c r="G4" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="H4" s="1"/>
+      <c r="K4">
+        <v>41</v>
+      </c>
       <c r="L4" s="1">
         <v>45</v>
       </c>
@@ -706,37 +716,37 @@
       <c r="S4" s="1">
         <v>999</v>
       </c>
-      <c r="T4" s="1"/>
       <c r="U4" s="1"/>
       <c r="V4" s="1"/>
       <c r="W4" s="1"/>
     </row>
     <row r="5" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A5" s="1" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="B5" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C5" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D5" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E5" s="4">
-        <v>35</v>
+        <v>16</v>
       </c>
       <c r="F5" s="4">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="G5" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
       <c r="H5" s="1"/>
-      <c r="K5" s="1"/>
-      <c r="L5" s="1"/>
+      <c r="L5" s="1">
+        <v>45</v>
+      </c>
       <c r="M5" s="1">
         <v>49</v>
       </c>
@@ -756,18 +766,16 @@
         <v>77</v>
       </c>
       <c r="S5" s="1">
-        <v>86</v>
-      </c>
-      <c r="T5" s="1">
-        <v>999</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="T5" s="1"/>
       <c r="U5" s="1"/>
       <c r="V5" s="1"/>
       <c r="W5" s="1"/>
     </row>
     <row r="6" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A6" s="1" t="s">
-        <v>15</v>
+        <v>13</v>
       </c>
       <c r="B6" s="1" t="s">
         <v>40</v>
@@ -779,10 +787,10 @@
         <v>9</v>
       </c>
       <c r="E6" s="4">
-        <v>40</v>
+        <v>35</v>
       </c>
       <c r="F6" s="4">
-        <v>44</v>
+        <v>39</v>
       </c>
       <c r="G6" s="5" t="b">
         <f>TRUE()</f>
@@ -821,7 +829,7 @@
     </row>
     <row r="7" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A7" s="1" t="s">
-        <v>16</v>
+        <v>15</v>
       </c>
       <c r="B7" s="1" t="s">
         <v>40</v>
@@ -833,10 +841,10 @@
         <v>9</v>
       </c>
       <c r="E7" s="4">
-        <v>45</v>
+        <v>40</v>
       </c>
       <c r="F7" s="4">
-        <v>49</v>
+        <v>44</v>
       </c>
       <c r="G7" s="5" t="b">
         <f>TRUE()</f>
@@ -875,7 +883,7 @@
     </row>
     <row r="8" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A8" s="1" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="B8" s="1" t="s">
         <v>40</v>
@@ -887,10 +895,10 @@
         <v>9</v>
       </c>
       <c r="E8" s="4">
-        <v>50</v>
+        <v>45</v>
       </c>
       <c r="F8" s="4">
-        <v>54</v>
+        <v>49</v>
       </c>
       <c r="G8" s="5" t="b">
         <f>TRUE()</f>
@@ -929,7 +937,7 @@
     </row>
     <row r="9" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A9" s="1" t="s">
-        <v>18</v>
+        <v>17</v>
       </c>
       <c r="B9" s="1" t="s">
         <v>40</v>
@@ -941,10 +949,10 @@
         <v>9</v>
       </c>
       <c r="E9" s="4">
-        <v>55</v>
+        <v>50</v>
       </c>
       <c r="F9" s="4">
-        <v>59</v>
+        <v>54</v>
       </c>
       <c r="G9" s="5" t="b">
         <f>TRUE()</f>
@@ -983,7 +991,7 @@
     </row>
     <row r="10" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A10" s="1" t="s">
-        <v>19</v>
+        <v>18</v>
       </c>
       <c r="B10" s="1" t="s">
         <v>40</v>
@@ -995,10 +1003,10 @@
         <v>9</v>
       </c>
       <c r="E10" s="4">
-        <v>60</v>
+        <v>55</v>
       </c>
       <c r="F10" s="4">
-        <v>64</v>
+        <v>59</v>
       </c>
       <c r="G10" s="5" t="b">
         <f>TRUE()</f>
@@ -1037,7 +1045,7 @@
     </row>
     <row r="11" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A11" s="1" t="s">
-        <v>20</v>
+        <v>19</v>
       </c>
       <c r="B11" s="1" t="s">
         <v>40</v>
@@ -1049,10 +1057,10 @@
         <v>9</v>
       </c>
       <c r="E11" s="4">
-        <v>65</v>
+        <v>60</v>
       </c>
       <c r="F11" s="4">
-        <v>69</v>
+        <v>64</v>
       </c>
       <c r="G11" s="5" t="b">
         <f>TRUE()</f>
@@ -1091,7 +1099,7 @@
     </row>
     <row r="12" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A12" s="1" t="s">
-        <v>21</v>
+        <v>20</v>
       </c>
       <c r="B12" s="1" t="s">
         <v>40</v>
@@ -1103,10 +1111,10 @@
         <v>9</v>
       </c>
       <c r="E12" s="4">
-        <v>70</v>
+        <v>65</v>
       </c>
       <c r="F12" s="4">
-        <v>74</v>
+        <v>69</v>
       </c>
       <c r="G12" s="5" t="b">
         <f>TRUE()</f>
@@ -1145,7 +1153,7 @@
     </row>
     <row r="13" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A13" s="1" t="s">
-        <v>22</v>
+        <v>21</v>
       </c>
       <c r="B13" s="1" t="s">
         <v>40</v>
@@ -1157,10 +1165,10 @@
         <v>9</v>
       </c>
       <c r="E13" s="4">
-        <v>75</v>
+        <v>70</v>
       </c>
       <c r="F13" s="4">
-        <v>999</v>
+        <v>74</v>
       </c>
       <c r="G13" s="5" t="b">
         <f>TRUE()</f>
@@ -1199,22 +1207,22 @@
     </row>
     <row r="14" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A14" s="1" t="s">
-        <v>23</v>
+        <v>22</v>
       </c>
       <c r="B14" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C14" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D14" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E14" s="4">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F14" s="4">
-        <v>20</v>
+        <v>999</v>
       </c>
       <c r="G14" s="5" t="b">
         <f>TRUE()</f>
@@ -1251,24 +1259,24 @@
       <c r="V14" s="1"/>
       <c r="W14" s="1"/>
     </row>
-    <row r="15" spans="1:23" ht="15" x14ac:dyDescent="0.2">
+    <row r="15" spans="1:23" ht="15.75" customHeight="1" x14ac:dyDescent="0.2">
       <c r="A15" s="1" t="s">
-        <v>25</v>
+        <v>23</v>
       </c>
       <c r="B15" s="1" t="s">
-        <v>25</v>
+        <v>39</v>
       </c>
       <c r="C15" s="1" t="s">
-        <v>26</v>
+        <v>24</v>
       </c>
       <c r="D15" s="1" t="s">
         <v>9</v>
       </c>
       <c r="E15" s="4">
-        <v>0</v>
+        <v>15</v>
       </c>
       <c r="F15" s="4">
-        <v>999</v>
+        <v>20</v>
       </c>
       <c r="G15" s="5" t="b">
         <f>TRUE()</f>
@@ -1307,66 +1315,61 @@
     </row>
     <row r="16" spans="1:23" ht="15" x14ac:dyDescent="0.2">
       <c r="A16" s="1" t="s">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="B16" s="1" t="s">
-        <v>38</v>
+        <v>25</v>
       </c>
       <c r="C16" s="1" t="s">
-        <v>8</v>
+        <v>26</v>
       </c>
       <c r="D16" s="1" t="s">
-        <v>27</v>
+        <v>9</v>
       </c>
       <c r="E16" s="4">
         <v>0</v>
       </c>
       <c r="F16" s="4">
-        <v>13</v>
+        <v>999</v>
       </c>
       <c r="G16" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H16" s="2">
-        <v>32</v>
-      </c>
-      <c r="I16" s="1">
-        <v>36</v>
-      </c>
-      <c r="J16">
-        <v>40</v>
-      </c>
-      <c r="K16">
-        <v>45</v>
-      </c>
-      <c r="L16" s="1">
-        <v>50</v>
-      </c>
+      <c r="H16" s="1"/>
+      <c r="K16" s="1"/>
+      <c r="L16" s="1"/>
       <c r="M16" s="1">
-        <v>55</v>
+        <v>49</v>
       </c>
       <c r="N16" s="1">
-        <v>60</v>
+        <v>53</v>
       </c>
       <c r="O16" s="1">
-        <v>65</v>
+        <v>57</v>
       </c>
       <c r="P16" s="1">
-        <v>70</v>
+        <v>61</v>
       </c>
       <c r="Q16" s="1">
-        <v>999</v>
-      </c>
-      <c r="R16" s="1"/>
-      <c r="S16" s="1"/>
-      <c r="T16" s="1"/>
+        <v>69</v>
+      </c>
+      <c r="R16" s="1">
+        <v>77</v>
+      </c>
+      <c r="S16" s="1">
+        <v>86</v>
+      </c>
+      <c r="T16" s="1">
+        <v>999</v>
+      </c>
       <c r="U16" s="1"/>
       <c r="V16" s="1"/>
+      <c r="W16" s="1"/>
     </row>
     <row r="17" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A17" s="1" t="s">
-        <v>11</v>
+        <v>41</v>
       </c>
       <c r="B17" s="1" t="s">
         <v>38</v>
@@ -1378,17 +1381,27 @@
         <v>27</v>
       </c>
       <c r="E17" s="4">
-        <v>14</v>
+        <v>0</v>
       </c>
       <c r="F17" s="4">
-        <v>15</v>
+        <v>11</v>
       </c>
       <c r="G17" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H17" s="2"/>
-      <c r="I17" s="1"/>
+      <c r="H17" s="2">
+        <v>32</v>
+      </c>
+      <c r="I17" s="1">
+        <v>36</v>
+      </c>
+      <c r="J17">
+        <v>40</v>
+      </c>
+      <c r="K17">
+        <v>45</v>
+      </c>
       <c r="L17" s="1">
         <v>50</v>
       </c>
@@ -1405,23 +1418,17 @@
         <v>70</v>
       </c>
       <c r="Q17" s="1">
-        <v>75</v>
-      </c>
-      <c r="R17" s="1">
-        <v>85</v>
-      </c>
-      <c r="S17" s="1">
-        <v>95</v>
-      </c>
-      <c r="T17" s="1">
-        <v>999</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="R17" s="1"/>
+      <c r="S17" s="1"/>
+      <c r="T17" s="1"/>
       <c r="U17" s="1"/>
       <c r="V17" s="1"/>
     </row>
     <row r="18" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A18" s="1" t="s">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="B18" s="1" t="s">
         <v>38</v>
@@ -1433,18 +1440,30 @@
         <v>27</v>
       </c>
       <c r="E18" s="4">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="F18" s="4">
-        <v>17</v>
+        <v>13</v>
       </c>
       <c r="G18" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H18" s="2"/>
-      <c r="K18" s="1"/>
-      <c r="L18" s="2"/>
+      <c r="H18" s="2">
+        <v>32</v>
+      </c>
+      <c r="I18" s="1">
+        <v>36</v>
+      </c>
+      <c r="J18">
+        <v>40</v>
+      </c>
+      <c r="K18">
+        <v>45</v>
+      </c>
+      <c r="L18" s="1">
+        <v>50</v>
+      </c>
       <c r="M18" s="1">
         <v>55</v>
       </c>
@@ -1458,66 +1477,62 @@
         <v>70</v>
       </c>
       <c r="Q18" s="1">
-        <v>75</v>
-      </c>
-      <c r="R18" s="1">
-        <v>85</v>
-      </c>
-      <c r="S18" s="1">
-        <v>95</v>
-      </c>
-      <c r="T18" s="1">
-        <v>999</v>
-      </c>
+        <v>999</v>
+      </c>
+      <c r="R18" s="1"/>
+      <c r="S18" s="1"/>
+      <c r="T18" s="1"/>
       <c r="U18" s="1"/>
       <c r="V18" s="1"/>
     </row>
     <row r="19" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A19" s="1" t="s">
-        <v>28</v>
+        <v>11</v>
       </c>
       <c r="B19" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C19" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D19" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E19" s="4">
-        <v>35</v>
+        <v>14</v>
       </c>
       <c r="F19" s="4">
-        <v>39</v>
+        <v>15</v>
       </c>
       <c r="G19" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H19" s="1"/>
-      <c r="K19" s="1"/>
-      <c r="L19" s="1"/>
+      <c r="H19" s="2"/>
+      <c r="I19" s="1"/>
+      <c r="L19" s="1">
+        <v>50</v>
+      </c>
       <c r="M19" s="1">
+        <v>55</v>
+      </c>
+      <c r="N19" s="1">
         <v>60</v>
       </c>
-      <c r="N19" s="1">
+      <c r="O19" s="1">
         <v>65</v>
       </c>
-      <c r="O19" s="1">
+      <c r="P19" s="1">
         <v>70</v>
       </c>
-      <c r="P19" s="1">
+      <c r="Q19" s="1">
         <v>75</v>
       </c>
-      <c r="Q19" s="1">
+      <c r="R19" s="1">
         <v>85</v>
       </c>
-      <c r="R19" s="1">
+      <c r="S19" s="1">
         <v>95</v>
-      </c>
-      <c r="S19" s="1">
-        <v>110</v>
       </c>
       <c r="T19" s="1">
         <v>999</v>
@@ -1527,50 +1542,50 @@
     </row>
     <row r="20" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A20" s="1" t="s">
-        <v>29</v>
+        <v>12</v>
       </c>
       <c r="B20" s="1" t="s">
-        <v>40</v>
+        <v>38</v>
       </c>
       <c r="C20" s="1" t="s">
-        <v>14</v>
+        <v>8</v>
       </c>
       <c r="D20" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E20" s="4">
-        <v>40</v>
+        <v>16</v>
       </c>
       <c r="F20" s="4">
-        <v>44</v>
+        <v>17</v>
       </c>
       <c r="G20" s="5" t="b">
         <f>TRUE()</f>
         <v>1</v>
       </c>
-      <c r="H20" s="1"/>
+      <c r="H20" s="2"/>
       <c r="K20" s="1"/>
-      <c r="L20" s="1"/>
+      <c r="L20" s="2"/>
       <c r="M20" s="1">
+        <v>55</v>
+      </c>
+      <c r="N20" s="1">
         <v>60</v>
       </c>
-      <c r="N20" s="1">
+      <c r="O20" s="1">
         <v>65</v>
       </c>
-      <c r="O20" s="1">
+      <c r="P20" s="1">
         <v>70</v>
       </c>
-      <c r="P20" s="1">
+      <c r="Q20" s="1">
         <v>75</v>
       </c>
-      <c r="Q20" s="1">
+      <c r="R20" s="1">
         <v>85</v>
       </c>
-      <c r="R20" s="1">
+      <c r="S20" s="1">
         <v>95</v>
-      </c>
-      <c r="S20" s="1">
-        <v>110</v>
       </c>
       <c r="T20" s="1">
         <v>999</v>
@@ -1580,7 +1595,7 @@
     </row>
     <row r="21" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A21" s="1" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="B21" s="1" t="s">
         <v>40</v>
@@ -1592,10 +1607,10 @@
         <v>27</v>
       </c>
       <c r="E21" s="4">
-        <v>45</v>
+        <v>35</v>
       </c>
       <c r="F21" s="4">
-        <v>49</v>
+        <v>39</v>
       </c>
       <c r="G21" s="5" t="b">
         <f>TRUE()</f>
@@ -1633,7 +1648,7 @@
     </row>
     <row r="22" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A22" s="1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
       <c r="B22" s="1" t="s">
         <v>40</v>
@@ -1645,10 +1660,10 @@
         <v>27</v>
       </c>
       <c r="E22" s="4">
-        <v>50</v>
+        <v>40</v>
       </c>
       <c r="F22" s="4">
-        <v>54</v>
+        <v>44</v>
       </c>
       <c r="G22" s="5" t="b">
         <f>TRUE()</f>
@@ -1686,7 +1701,7 @@
     </row>
     <row r="23" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A23" s="1" t="s">
-        <v>32</v>
+        <v>30</v>
       </c>
       <c r="B23" s="1" t="s">
         <v>40</v>
@@ -1698,10 +1713,10 @@
         <v>27</v>
       </c>
       <c r="E23" s="4">
-        <v>55</v>
+        <v>45</v>
       </c>
       <c r="F23" s="4">
-        <v>59</v>
+        <v>49</v>
       </c>
       <c r="G23" s="5" t="b">
         <f>TRUE()</f>
@@ -1739,7 +1754,7 @@
     </row>
     <row r="24" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A24" s="1" t="s">
-        <v>33</v>
+        <v>31</v>
       </c>
       <c r="B24" s="1" t="s">
         <v>40</v>
@@ -1751,10 +1766,10 @@
         <v>27</v>
       </c>
       <c r="E24" s="4">
-        <v>60</v>
+        <v>50</v>
       </c>
       <c r="F24" s="4">
-        <v>64</v>
+        <v>54</v>
       </c>
       <c r="G24" s="5" t="b">
         <f>TRUE()</f>
@@ -1792,7 +1807,7 @@
     </row>
     <row r="25" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A25" s="1" t="s">
-        <v>34</v>
+        <v>32</v>
       </c>
       <c r="B25" s="1" t="s">
         <v>40</v>
@@ -1804,10 +1819,10 @@
         <v>27</v>
       </c>
       <c r="E25" s="4">
-        <v>65</v>
+        <v>55</v>
       </c>
       <c r="F25" s="4">
-        <v>69</v>
+        <v>59</v>
       </c>
       <c r="G25" s="5" t="b">
         <f>TRUE()</f>
@@ -1845,7 +1860,7 @@
     </row>
     <row r="26" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A26" s="1" t="s">
-        <v>35</v>
+        <v>33</v>
       </c>
       <c r="B26" s="1" t="s">
         <v>40</v>
@@ -1857,10 +1872,10 @@
         <v>27</v>
       </c>
       <c r="E26" s="4">
-        <v>70</v>
+        <v>60</v>
       </c>
       <c r="F26" s="4">
-        <v>74</v>
+        <v>64</v>
       </c>
       <c r="G26" s="5" t="b">
         <f>TRUE()</f>
@@ -1898,7 +1913,7 @@
     </row>
     <row r="27" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A27" s="1" t="s">
-        <v>36</v>
+        <v>34</v>
       </c>
       <c r="B27" s="1" t="s">
         <v>40</v>
@@ -1910,10 +1925,10 @@
         <v>27</v>
       </c>
       <c r="E27" s="4">
-        <v>75</v>
+        <v>65</v>
       </c>
       <c r="F27" s="4">
-        <v>79</v>
+        <v>69</v>
       </c>
       <c r="G27" s="5" t="b">
         <f>TRUE()</f>
@@ -1950,8 +1965,8 @@
       <c r="V27" s="1"/>
     </row>
     <row r="28" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A28" s="6" t="s">
-        <v>37</v>
+      <c r="A28" s="1" t="s">
+        <v>35</v>
       </c>
       <c r="B28" s="1" t="s">
         <v>40</v>
@@ -1963,10 +1978,10 @@
         <v>27</v>
       </c>
       <c r="E28" s="4">
-        <v>80</v>
+        <v>70</v>
       </c>
       <c r="F28" s="4">
-        <v>999</v>
+        <v>74</v>
       </c>
       <c r="G28" s="5" t="b">
         <f>TRUE()</f>
@@ -2004,22 +2019,22 @@
     </row>
     <row r="29" spans="1:22" ht="15" x14ac:dyDescent="0.2">
       <c r="A29" s="1" t="s">
-        <v>23</v>
+        <v>36</v>
       </c>
       <c r="B29" s="1" t="s">
-        <v>39</v>
+        <v>40</v>
       </c>
       <c r="C29" s="1" t="s">
-        <v>24</v>
+        <v>14</v>
       </c>
       <c r="D29" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E29" s="4">
-        <v>15</v>
+        <v>75</v>
       </c>
       <c r="F29" s="4">
-        <v>20</v>
+        <v>79</v>
       </c>
       <c r="G29" s="5" t="b">
         <f>TRUE()</f>
@@ -2056,20 +2071,20 @@
       <c r="V29" s="1"/>
     </row>
     <row r="30" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="A30" s="1" t="s">
-        <v>25</v>
+      <c r="A30" s="6" t="s">
+        <v>37</v>
       </c>
       <c r="B30" s="1" t="s">
-        <v>25</v>
+        <v>40</v>
       </c>
       <c r="C30" s="1" t="s">
-        <v>26</v>
+        <v>14</v>
       </c>
       <c r="D30" s="1" t="s">
         <v>27</v>
       </c>
       <c r="E30" s="4">
-        <v>0</v>
+        <v>80</v>
       </c>
       <c r="F30" s="4">
         <v>999</v>
@@ -2109,24 +2124,110 @@
       <c r="V30" s="1"/>
     </row>
     <row r="31" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="M31" s="1"/>
-      <c r="N31" s="1"/>
-      <c r="O31" s="1"/>
-      <c r="P31" s="1"/>
-      <c r="Q31" s="1"/>
-      <c r="R31" s="1"/>
-      <c r="S31" s="1"/>
-      <c r="T31" s="1"/>
+      <c r="A31" s="1" t="s">
+        <v>23</v>
+      </c>
+      <c r="B31" s="1" t="s">
+        <v>39</v>
+      </c>
+      <c r="C31" s="1" t="s">
+        <v>24</v>
+      </c>
+      <c r="D31" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E31" s="4">
+        <v>15</v>
+      </c>
+      <c r="F31" s="4">
+        <v>20</v>
+      </c>
+      <c r="G31" s="5" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H31" s="1"/>
+      <c r="K31" s="1"/>
+      <c r="L31" s="1"/>
+      <c r="M31" s="1">
+        <v>60</v>
+      </c>
+      <c r="N31" s="1">
+        <v>65</v>
+      </c>
+      <c r="O31" s="1">
+        <v>70</v>
+      </c>
+      <c r="P31" s="1">
+        <v>75</v>
+      </c>
+      <c r="Q31" s="1">
+        <v>85</v>
+      </c>
+      <c r="R31" s="1">
+        <v>95</v>
+      </c>
+      <c r="S31" s="1">
+        <v>110</v>
+      </c>
+      <c r="T31" s="1">
+        <v>999</v>
+      </c>
+      <c r="U31" s="1"/>
+      <c r="V31" s="1"/>
     </row>
     <row r="32" spans="1:22" ht="15" x14ac:dyDescent="0.2">
-      <c r="M32" s="1"/>
-      <c r="N32" s="1"/>
-      <c r="O32" s="1"/>
-      <c r="P32" s="1"/>
-      <c r="Q32" s="1"/>
-      <c r="R32" s="1"/>
-      <c r="S32" s="1"/>
-      <c r="T32" s="1"/>
+      <c r="A32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="B32" s="1" t="s">
+        <v>25</v>
+      </c>
+      <c r="C32" s="1" t="s">
+        <v>26</v>
+      </c>
+      <c r="D32" s="1" t="s">
+        <v>27</v>
+      </c>
+      <c r="E32" s="4">
+        <v>0</v>
+      </c>
+      <c r="F32" s="4">
+        <v>999</v>
+      </c>
+      <c r="G32" s="5" t="b">
+        <f>TRUE()</f>
+        <v>1</v>
+      </c>
+      <c r="H32" s="1"/>
+      <c r="K32" s="1"/>
+      <c r="L32" s="1"/>
+      <c r="M32" s="1">
+        <v>60</v>
+      </c>
+      <c r="N32" s="1">
+        <v>65</v>
+      </c>
+      <c r="O32" s="1">
+        <v>70</v>
+      </c>
+      <c r="P32" s="1">
+        <v>75</v>
+      </c>
+      <c r="Q32" s="1">
+        <v>85</v>
+      </c>
+      <c r="R32" s="1">
+        <v>95</v>
+      </c>
+      <c r="S32" s="1">
+        <v>110</v>
+      </c>
+      <c r="T32" s="1">
+        <v>999</v>
+      </c>
+      <c r="U32" s="1"/>
+      <c r="V32" s="1"/>
     </row>
     <row r="33" spans="13:20" ht="15" x14ac:dyDescent="0.2">
       <c r="M33" s="1"/>
@@ -2148,6 +2249,26 @@
       <c r="S34" s="1"/>
       <c r="T34" s="1"/>
     </row>
+    <row r="35" spans="13:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="M35" s="1"/>
+      <c r="N35" s="1"/>
+      <c r="O35" s="1"/>
+      <c r="P35" s="1"/>
+      <c r="Q35" s="1"/>
+      <c r="R35" s="1"/>
+      <c r="S35" s="1"/>
+      <c r="T35" s="1"/>
+    </row>
+    <row r="36" spans="13:20" ht="15" x14ac:dyDescent="0.2">
+      <c r="M36" s="1"/>
+      <c r="N36" s="1"/>
+      <c r="O36" s="1"/>
+      <c r="P36" s="1"/>
+      <c r="Q36" s="1"/>
+      <c r="R36" s="1"/>
+      <c r="S36" s="1"/>
+      <c r="T36" s="1"/>
+    </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.511811023622047" footer="0.511811023622047"/>
   <pageSetup orientation="portrait" horizontalDpi="300" verticalDpi="300"/>
